--- a/data/xlsx/journal_indexing.xlsx
+++ b/data/xlsx/journal_indexing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3114,6 +3114,34 @@
         </is>
       </c>
     </row>
+    <row r="49" hidden="0">
+      <c r="A49" t="str">
+        <v>International Journal of Music Mediation (IJMM)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2943-6109 (online)</v>
+      </c>
+      <c r="C49" t="str">
+        <v>mdwPress / university publisher</v>
+      </c>
+      <c r="D49" t="str">
+        <v>https://ijmm.world/ijmm/about/submissions</v>
+      </c>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49" t="str">
+        <v>Diamond open access; no APCs; CC BY-NC 4.0</v>
+      </c>
+      <c r="J49" t="str">
+        <v>WorldCat; Google Scholar; BASE (journal-reported)</v>
+      </c>
+      <c r="K49"/>
+      <c r="L49" t="str">
+        <v>Verified 2026-10-13. Unverified indexing fields left blank (including DOAJ membership). Sources: https://ijmm.world/ ; https://ijmm.world/ijmm/policies_and_guidelines ; https://ijmm.world/ijmm/about/editorialTeam</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
